--- a/outputs/08/Ezine_Hibrit_Finansal_Model.xlsx
+++ b/outputs/08/Ezine_Hibrit_Finansal_Model.xlsx
@@ -2720,7 +2720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2924,11 +2924,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.49</v>
+        <v>-1.66</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P(NPV&gt;0) %50 · CVaR %5 -25.8 M$ · azami prim 1.49 M$</t>
+          <t>P(NPV&gt;0) %42 · CVaR %5 -28.0 M$ · azami prim 0.00 M$</t>
         </is>
       </c>
     </row>
@@ -2939,11 +2939,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.13</v>
+        <v>0.43</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>P(NPV&gt;0) %54 · CVaR %5 -20.5 M$ · azami prim 3.13 M$</t>
+          <t>P(NPV&gt;0) %46 · CVaR %5 -22.2 M$ · azami prim 0.43 M$</t>
         </is>
       </c>
     </row>
@@ -2954,11 +2954,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-10.91</v>
+        <v>-12.25</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>P(NPV&gt;0) %14 · CVaR %5 -28.6 M$ · azami prim 0.00 M$</t>
+          <t>P(NPV&gt;0) %12 · CVaR %5 -29.7 M$ · azami prim 0.00 M$</t>
         </is>
       </c>
     </row>
@@ -2969,11 +2969,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-3.98</v>
+        <v>-6.05</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>P(NPV&gt;0) %34 · CVaR %5 -24.3 M$ · azami prim 0.00 M$</t>
+          <t>P(NPV&gt;0) %28 · CVaR %5 -26.0 M$ · azami prim 0.00 M$</t>
         </is>
       </c>
     </row>
@@ -2984,11 +2984,184 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.15</v>
+        <v>-2.11</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>P(NPV&gt;0) %50 · CVaR %5 -27.8 M$ · azami prim 1.15 M$</t>
+          <t>P(NPV&gt;0) %42 · CVaR %5 -30.4 M$ · azami prim 0.00 M$</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>Deterministik → Monte Carlo köprüsü (outputs/07/fark_ayristirma_sonra.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Deterministik baz (58 USD/MWh sabit, COD 2030)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fiyat ortalaması sapması</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>(i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Fiyat oynaklığı: batarya (arbitraj + SFK) gelirleri</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>(iii)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Fiyat oynaklığı: vergi, mahsup ve diğer satırlar</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>(iv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Kriz yıllarında düzenleyici tavan</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>(iv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>YEKDEM yıllık opsiyonu (dışbükeylik)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>(ii)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SFK doyum senaryoları (karışım ≠ baz yol)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>(iii)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Hava, model hatası, kanibalizasyon, kesinti</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>(v)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CAPEX / OPEX / bozunma belirsizliği</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>(iv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Takvim: COD 2030 → 2029-11 (P50)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Monte Carlo beklenen NPV (baz vaka)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
